--- a/output/神奈川静岡_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/神奈川静岡_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -451,11 +451,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>4</v>
@@ -709,7 +709,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>

--- a/output/神奈川静岡_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/神奈川静岡_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -512,7 +512,7 @@
         <v>116</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr">
@@ -691,7 +691,7 @@
         <v>253</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -779,35 +779,35 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>富士フイルム製画像読み取り装置及び回診用X 線撮影の保守契約の更新</t>
+          <t>X線透視撮影装置導入に伴う追加備品等一式</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>令和7年8月30日</t>
+          <t>令和5年9月12日</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>10561452</v>
+        <v>6290900</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>富士フイルムメディカル株式会社南関東支社神奈川県横浜市西区高島1-2-13</t>
+          <t>株式会社島津製作所横浜支店横浜市西区北幸2-8-29</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://www.yokohama.jrc.or.jp/wp/wp-content/uploads/2025/10/随意契約の公表（令和7年度）.pdf</t>
+          <t>https://www.yokohama.jrc.or.jp/wp/wp-content/uploads/2024/10/令和5年度_随意契約の公表.pdf</t>
         </is>
       </c>
     </row>
@@ -819,21 +819,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>相模原赤十字病院</t>
+          <t>横浜市立みなと赤十字病院</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>一般X線撮影装置修理（X線管球交換・ハンドスイッチ交換）</t>
+          <t>富士フイルム製画像読み取り装置及び回診用X 線撮影の保守契約の更新</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>令和8年4月16日</t>
+          <t>令和7年8月30日</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2727967</v>
+        <v>10561452</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>キャノンメディカルシステムズ株式会社神奈川県横浜市西区高島2丁目6番32号 横浜東ロウィスポートビル</t>
+          <t>富士フイルムメディカル株式会社南関東支社神奈川県横浜市西区高島1-2-13</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>http://www.sagamihara.jrc.or.jp/wp/wp-content/uploads/2026/06/随意契約締結状況（R8年度）4月分.pdf</t>
+          <t>https://www.yokohama.jrc.or.jp/wp/wp-content/uploads/2025/10/随意契約の公表（令和7年度）.pdf</t>
         </is>
       </c>
     </row>
@@ -869,16 +869,16 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>DR装置（2014年1月設置分）</t>
+          <t>一般X線撮影装置修理（X線管球交換・ハンドスイッチ交換）</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>令和8年3月31日</t>
+          <t>令和8年4月16日</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2603700</v>
+        <v>2727967</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -887,62 +887,107 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>富士フイルムメディカル株式会社 南関東支社神奈川県横浜市西区高島1-2-13LG YOKOHAMA INNOVATIONCENTER 10F</t>
+          <t>キャノンメディカルシステムズ株式会社神奈川県横浜市西区高島2丁目6番32号 横浜東ロウィスポートビル</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>http://www.sagamihara.jrc.or.jp/wp/wp-content/uploads/2026/04/随意契約締結状況（R7年度）3月分.pdf</t>
+          <t>http://www.sagamihara.jrc.or.jp/wp/wp-content/uploads/2026/06/随意契約締結状況（R8年度）4月分.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>相模原赤十字病院</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>DR装置（2014年1月設置分）</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>令和8年3月31日</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2603700</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>富士フイルムメディカル株式会社 南関東支社神奈川県横浜市西区高島1-2-13LG YOKOHAMA INNOVATIONCENTER 10F</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>http://www.sagamihara.jrc.or.jp/wp/wp-content/uploads/2026/04/随意契約締結状況（R7年度）3月分.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
           <t>静岡県</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>静岡赤十字病院</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>移動型Ｘ線撮影装置Sirius Starmobile tiara airy</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>令和4年12月9日</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>製品</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>エム・シー・ヘルスケア（株）東京都港区港南2丁目16-1</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>https://www.shizuoka-med.jrc.or.jp/medical/bid/file/3141/bid260.pdf</t>
         </is>

--- a/output/神奈川静岡_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/神奈川静岡_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
